--- a/MSC_mean.xlsx
+++ b/MSC_mean.xlsx
@@ -69,7 +69,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C569"/>
+  <dimension ref="A1:C577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1859,7 +1859,7 @@
         <v>33390</v>
       </c>
       <c r="B163" s="2">
-        <v>3.5691056910569321</v>
+        <v>3.561866125760639</v>
       </c>
       <c r="C163" s="2">
         <v>3</v>
@@ -6204,7 +6204,7 @@
         <v>45413</v>
       </c>
       <c r="B558" s="2">
-        <v>3.8117489948181169</v>
+        <v>3.7543231619330721</v>
       </c>
       <c r="C558" s="2">
         <v>3</v>
@@ -6215,7 +6215,7 @@
         <v>45444</v>
       </c>
       <c r="B559" s="2">
-        <v>3.4167823221387024</v>
+        <v>3.5426782535649366</v>
       </c>
       <c r="C559" s="2">
         <v>3</v>
@@ -6259,10 +6259,10 @@
         <v>45566</v>
       </c>
       <c r="B563" s="2">
-        <v>2.6514813566866446</v>
+        <v>2.8835096969727996</v>
       </c>
       <c r="C563" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -6270,7 +6270,7 @@
         <v>45597</v>
       </c>
       <c r="B564" s="2">
-        <v>2.0227370817075117</v>
+        <v>2.229239689827569</v>
       </c>
       <c r="C564" s="2">
         <v>2</v>
@@ -6281,7 +6281,7 @@
         <v>45627</v>
       </c>
       <c r="B565" s="2">
-        <v>2.1889736559211377</v>
+        <v>2.0253867200746996</v>
       </c>
       <c r="C565" s="2">
         <v>3</v>
@@ -6292,7 +6292,7 @@
         <v>45658</v>
       </c>
       <c r="B566" s="2">
-        <v>3.7109657582482223</v>
+        <v>3.6923752061763357</v>
       </c>
       <c r="C566" s="2">
         <v>3</v>
@@ -6303,7 +6303,7 @@
         <v>45689</v>
       </c>
       <c r="B567" s="2">
-        <v>4.0326228841318468</v>
+        <v>4.0154156768139693</v>
       </c>
       <c r="C567" s="2">
         <v>3</v>
@@ -6314,7 +6314,7 @@
         <v>45717</v>
       </c>
       <c r="B568" s="2">
-        <v>5.1144120461002753</v>
+        <v>5.1237102027216661</v>
       </c>
       <c r="C568" s="2">
         <v>5</v>
@@ -6325,11 +6325,95 @@
         <v>45748</v>
       </c>
       <c r="B569" s="2">
-        <v>6.0429111069797754</v>
+        <v>6.0191855433043564</v>
       </c>
       <c r="C569" s="2">
         <v>5</v>
       </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B570" s="2">
+        <v>6.6832431497695293</v>
+      </c>
+      <c r="C570" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B571" s="2">
+        <v>5.4589704280148599</v>
+      </c>
+      <c r="C571" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B572" s="2">
+        <v>4.7152336488914788</v>
+      </c>
+      <c r="C572" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B573" s="2">
+        <v>5.4237211191704109</v>
+      </c>
+      <c r="C573" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B574" s="2">
+        <v>5.2364435014466331</v>
+      </c>
+      <c r="C574" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B575" s="2">
+        <v>5.4147373567711812</v>
+      </c>
+      <c r="C575" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B576" s="2">
+        <v>4.3374477647767007</v>
+      </c>
+      <c r="C576" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B577" s="2"/>
+      <c r="C577" s="2"/>
     </row>
   </sheetData>
 </worksheet>
